--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104525_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104525_W8.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.0327</v>
+        <v>8.0228</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8784</v>
+        <v>4.2421</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1543</v>
+        <v>3.7808</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3602</v>
+        <v>3.3661</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1052</v>
+        <v>1.1139</v>
       </c>
       <c r="I2" t="n">
-        <v>2.255</v>
+        <v>2.2522</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7514</v>
+        <v>2.7324</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4778</v>
+        <v>0.4686</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2736</v>
+        <v>2.2638</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6088</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5403</v>
+        <v>0.517</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0344</v>
+        <v>0.4202</v>
       </c>
       <c r="U2" t="n">
-        <v>0.506</v>
+        <v>0.0969</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8959</v>
+        <v>6.9028</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2889</v>
+        <v>4.012</v>
       </c>
       <c r="F3" t="n">
-        <v>2.607</v>
+        <v>2.8908</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3682</v>
+        <v>6.3451</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0883</v>
+        <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2799</v>
+        <v>6.2724</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6339</v>
+        <v>5.5824</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0355</v>
+        <v>-0.0699</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6694</v>
+        <v>5.6523</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7343</v>
+        <v>0.7627</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1113</v>
+        <v>-0.0765</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9648</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0761</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2848</v>
+        <v>5.486</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2723</v>
+        <v>3.4803</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0125</v>
+        <v>2.0057</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2577</v>
+        <v>2.25</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5411</v>
+        <v>-0.5427</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7988</v>
+        <v>2.7928</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3289</v>
+        <v>2.3062</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4298</v>
+        <v>-0.4417</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7587</v>
+        <v>2.7479</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0712</v>
+        <v>-0.0562</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4927</v>
+        <v>-0.2892</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2029</v>
+        <v>0.171</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0648</v>
+        <v>3.7253</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1862</v>
+        <v>0.8002</v>
       </c>
       <c r="F5" t="n">
-        <v>3.251</v>
+        <v>2.9251</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5965</v>
+        <v>1.5992</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1327</v>
+        <v>1.1344</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4638</v>
+        <v>0.4648</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9867</v>
+        <v>1.9549</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5443</v>
+        <v>1.5233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4424</v>
+        <v>0.4315</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3902</v>
+        <v>-0.3557</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4116</v>
+        <v>-0.389</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6224</v>
+        <v>0.0351</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9557</v>
+        <v>0.0809</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3333</v>
+        <v>-0.0458</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4734</v>
+        <v>1.6659</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1611</v>
+        <v>1.3264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3123</v>
+        <v>0.3395</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4665</v>
+        <v>0.4781</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9275</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4584</v>
+        <v>-0.4495</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4063</v>
+        <v>1.3933</v>
       </c>
       <c r="K6" t="n">
-        <v>1.257</v>
+        <v>1.2443</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9398</v>
+        <v>-0.9152</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5414</v>
+        <v>-0.3553</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0212</v>
+        <v>0.2111</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5626</v>
+        <v>-0.5664</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7587</v>
+        <v>1.2419</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2612</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4975</v>
+        <v>1.9178</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4615</v>
+        <v>2.777</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.6637</v>
+        <v>1.3696</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2021</v>
+        <v>1.4073</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1936</v>
+        <v>2.9895</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1584</v>
+        <v>1.672</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9648</v>
+        <v>1.3175</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.268</v>
+        <v>-0.2125</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5053</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2373</v>
+        <v>0.0898</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9488</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q7" t="n">
+        <v>-4.5526</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.5039</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.5759</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.2023</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.3736</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.0895</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.0895</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.9488</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.8462</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.4548</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.6085</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.5748</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.5748</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.919</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1246</v>
+        <v>0.1621</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7007</v>
+        <v>0.7569</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7788</v>
+        <v>1.1621</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3635</v>
+        <v>-0.1155</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4153</v>
+        <v>1.2777</v>
       </c>
       <c r="J8" t="n">
-        <v>3.015</v>
+        <v>1.0035</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6797</v>
+        <v>0.2446</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3353</v>
+        <v>0.759</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2362</v>
+        <v>0.1586</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3162</v>
+        <v>-0.3601</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08</v>
+        <v>0.5187</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4952</v>
+        <v>3.4145</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2539</v>
+        <v>-0.4983</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6956</v>
+        <v>0.1389</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5583</v>
+        <v>-0.6372</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-2.0212</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5074</v>
+        <v>0.8873</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.764</v>
+        <v>-0.5884</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2713</v>
+        <v>1.4757</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8589</v>
+        <v>1.8605</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6724</v>
+        <v>1.6743</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4912</v>
+        <v>0.4825</v>
       </c>
       <c r="K9" t="n">
-        <v>1.091</v>
+        <v>1.0859</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3678</v>
+        <v>1.378</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5814</v>
+        <v>0.5884</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4857</v>
+        <v>-0.1114</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.121</v>
+        <v>0.0673</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3648</v>
+        <v>-0.1786</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3826</v>
+        <v>0.3703</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1146</v>
+        <v>1.0296</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4972</v>
+        <v>-0.6593</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1602</v>
+        <v>1.6088</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1272</v>
+        <v>1.3212</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2874</v>
+        <v>0.2876</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0282</v>
+        <v>2.0822</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2526</v>
+        <v>1.8961</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7755</v>
+        <v>0.1862</v>
       </c>
       <c r="M10" t="n">
-        <v>0.132</v>
+        <v>-0.4734</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3798</v>
+        <v>-0.5749</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5118</v>
+        <v>0.1014</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2683</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4025</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0213</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1693</v>
+        <v>-0.1813</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.852</v>
+        <v>0.1721</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>-0.7739</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>1.405</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1928</v>
+        <v>-0.1031</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7503</v>
+        <v>-0.708</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5575</v>
+        <v>0.605</v>
       </c>
       <c r="G11" t="n">
-        <v>1.607</v>
+        <v>-1.4646</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3218</v>
+        <v>-2.6652</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2852</v>
+        <v>1.2006</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0914</v>
+        <v>-1.2232</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9048</v>
+        <v>-2.1761</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1866</v>
+        <v>0.9528</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4844</v>
+        <v>-0.2414</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5831</v>
+        <v>-0.4891</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2477</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>2.9592</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>2.9592</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1893</v>
+        <v>-0.0349</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4869</v>
+        <v>0.5152</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2976</v>
+        <v>-0.5501</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7712</v>
+        <v>-1.5628</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-1.5628</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5454</v>
+        <v>-0.4392</v>
       </c>
       <c r="E12" t="n">
-        <v>1.035</v>
+        <v>1.1019</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5804</v>
+        <v>-1.5411</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4387</v>
+        <v>0.44</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3449</v>
+        <v>-0.3419</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1741</v>
+        <v>1.1716</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7315</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1183</v>
+        <v>-0.0174</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1391</v>
+        <v>-0.0697</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>27.6238</v>
+        <v>28.679</v>
       </c>
       <c r="E13" t="n">
-        <v>13.4578</v>
+        <v>14.1823</v>
       </c>
       <c r="F13" t="n">
-        <v>14.1659</v>
+        <v>14.4969</v>
       </c>
       <c r="G13" t="n">
-        <v>20.4312</v>
+        <v>20.4223</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9319</v>
+        <v>3.948300000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>16.4994</v>
+        <v>16.4741</v>
       </c>
       <c r="J13" t="n">
-        <v>20.7135</v>
+        <v>20.4753</v>
       </c>
       <c r="K13" t="n">
-        <v>5.6008</v>
+        <v>5.4643</v>
       </c>
       <c r="L13" t="n">
-        <v>15.1126</v>
+        <v>15.0107</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2823000000000002</v>
+        <v>-0.05300000000000016</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.669</v>
+        <v>-1.5163</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3865</v>
+        <v>1.4631</v>
       </c>
       <c r="P13" t="n">
-        <v>7.938900000000001</v>
+        <v>7.966899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0126</v>
+        <v>-17.0725</v>
       </c>
       <c r="R13" t="n">
-        <v>24.9516</v>
+        <v>25.0395</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4498</v>
+        <v>-1.4161</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2120000000000003</v>
+        <v>1.2747</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.6616</v>
+        <v>-2.6905</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7033</v>
+        <v>1.7056</v>
       </c>
       <c r="W13" t="n">
-        <v>9.545</v>
+        <v>9.5047</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.841699999999999</v>
+        <v>-7.798999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3414</v>
+        <v>5.0665</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3014</v>
+        <v>4.5726</v>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>0.4939</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0312</v>
+        <v>1.0386</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8787</v>
+        <v>1.8784</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8476</v>
+        <v>-0.8398</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7024</v>
+        <v>1.6947</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6278</v>
+        <v>1.6203</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6712</v>
+        <v>-0.6562</v>
       </c>
       <c r="N14" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8715</v>
+        <v>0.6017</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2945</v>
+        <v>0.5898</v>
       </c>
       <c r="U14" t="n">
-        <v>0.577</v>
+        <v>0.0119</v>
       </c>
       <c r="V14" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W14" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8379</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0089</v>
+        <v>1.3583</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8467</v>
+        <v>-1.9879</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1917</v>
+        <v>0.1952</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0793</v>
+        <v>1.0799</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8847</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2175</v>
+        <v>1.2121</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1429</v>
+        <v>1.1376</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0258</v>
+        <v>-1.0169</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3826</v>
+        <v>0.5819</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2087</v>
+        <v>0.1462</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5913</v>
+        <v>0.4356</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>J. JACKSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8945</v>
+        <v>-1.1475</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1852</v>
+        <v>-0.3093</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7093</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2774</v>
+        <v>1.029</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.779</v>
+        <v>-0.9858</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4984</v>
+        <v>2.0147</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3501</v>
+        <v>2.806</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1323</v>
+        <v>0.1929</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4824</v>
+        <v>2.6131</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6275</v>
+        <v>-1.777</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-1.1786</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9808</v>
+        <v>-0.5984</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2902</v>
+        <v>-0.2369</v>
       </c>
       <c r="T16" t="n">
-        <v>1.733</v>
+        <v>0.1901</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4428</v>
+        <v>-0.427</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JACKSON</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3603</v>
+        <v>-1.5019</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4923</v>
+        <v>-0.6619</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8681</v>
+        <v>-0.84</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0337</v>
+        <v>-2.6331</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9973</v>
+        <v>-1.9436</v>
       </c>
       <c r="I17" t="n">
-        <v>2.031</v>
+        <v>-0.6895</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8394</v>
+        <v>-0.0994</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2007</v>
+        <v>-1.6557</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6387</v>
+        <v>1.5563</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8056</v>
+        <v>-2.5337</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.198</v>
+        <v>-0.2879</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6077</v>
+        <v>-2.2458</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.1757</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4718</v>
+        <v>1.0614</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0484</v>
+        <v>0.5757</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4234</v>
+        <v>0.4857</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2534</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3756</v>
+        <v>-1.7058</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.263</v>
+        <v>-0.4106</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1126</v>
+        <v>-1.2952</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4186</v>
+        <v>-2.4106</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3391</v>
+        <v>-1.3384</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1811</v>
+        <v>0.1545</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2211</v>
+        <v>0.1994</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5996</v>
+        <v>-2.5651</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6554</v>
+        <v>0.3194</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5293</v>
+        <v>0.4153</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1261</v>
+        <v>-0.0959</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4508</v>
+        <v>-1.7231</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3907</v>
+        <v>-1.1652</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0601</v>
+        <v>-0.5579</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.622</v>
+        <v>-1.2864</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.929</v>
+        <v>-0.792</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.4944</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0641</v>
+        <v>0.3171</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6287</v>
+        <v>-0.1594</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5646</v>
+        <v>0.4764</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5579</v>
+        <v>-1.6034</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3003</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2576</v>
+        <v>-0.9708</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1051</v>
+        <v>0.4738</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8075</v>
+        <v>0.794</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2976</v>
+        <v>-0.3202</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6709</v>
+        <v>-1.999</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2786</v>
+        <v>-2.8173</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6077</v>
+        <v>0.8183</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0773</v>
+        <v>-2.07</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4647</v>
+        <v>-0.4598</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6126</v>
+        <v>-1.6102</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4488</v>
+        <v>-1.4559</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.6141</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8865</v>
+        <v>-0.2265</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6956</v>
+        <v>-0.2232</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1909</v>
+        <v>-0.0033</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9562</v>
+        <v>-2.5746</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0631</v>
+        <v>-2.0816</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8931</v>
+        <v>-0.493</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6039</v>
+        <v>-3.6067</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2078</v>
+        <v>0.2068</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.8117</v>
+        <v>-3.8135</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.245</v>
+        <v>-2.2623</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.359</v>
+        <v>-1.3444</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.235</v>
+        <v>0.1427</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0212</v>
+        <v>0.0229</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2562</v>
+        <v>0.1198</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3544</v>
+        <v>-3.5155</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3571</v>
+        <v>-1.7349</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9973</v>
+        <v>-1.7806</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8108</v>
+        <v>-2.8087</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4328</v>
+        <v>-1.4386</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.378</v>
+        <v>-1.3701</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0506</v>
+        <v>-0.0709</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1252</v>
+        <v>-0.1454</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7602</v>
+        <v>-2.7378</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3203</v>
+        <v>0.1566</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5989</v>
+        <v>0.2481</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2786</v>
+        <v>-0.0915</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9058</v>
+        <v>-3.8815</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5118</v>
+        <v>-0.8348</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.394</v>
+        <v>-3.0467</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8228</v>
+        <v>-0.8085</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1401</v>
+        <v>-1.132</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3172</v>
+        <v>0.3235</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3729</v>
+        <v>0.366</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3361</v>
+        <v>-0.3415</v>
       </c>
       <c r="L23" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1957</v>
+        <v>-1.1745</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9073</v>
+        <v>0.1138</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>0.0834</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2813</v>
+        <v>0.0305</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9604</v>
+        <v>-5.6969</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1702</v>
+        <v>-5.3771</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7903</v>
+        <v>-0.3199</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2735</v>
+        <v>-3.2708</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3059</v>
+        <v>1.3067</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.5794</v>
+        <v>-4.5775</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5901</v>
+        <v>-0.608</v>
       </c>
       <c r="K24" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6834</v>
+        <v>-2.6628</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.2576</v>
+        <v>-2.2458</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2579</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0434</v>
+        <v>-0.2164</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2144</v>
+        <v>0.2243</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1984</v>
+        <v>-7.5348</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.0856</v>
+        <v>-5.3506</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1128</v>
+        <v>-2.1842</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.7815</v>
+        <v>-3.7902</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3216</v>
+        <v>-0.3298</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.4599</v>
+        <v>-3.4604</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.9825</v>
+        <v>-2.0009</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4471</v>
+        <v>-0.4589</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.799</v>
+        <v>-1.7893</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.9245</v>
+        <v>-1.9184</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5831</v>
+        <v>0.2554</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2994</v>
+        <v>0.0648</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2837</v>
+        <v>0.1906</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-27.6238</v>
+        <v>-26.8436</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.4873</v>
+        <v>-14.8124</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.1366</v>
+        <v>-12.0314</v>
       </c>
       <c r="G26" t="n">
-        <v>-20.4312</v>
+        <v>-20.4222</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.9319</v>
+        <v>-3.948199999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-16.4995</v>
+        <v>-16.4741</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2822999999999993</v>
+        <v>0.05299999999999994</v>
       </c>
       <c r="K26" t="n">
-        <v>1.6691</v>
+        <v>1.5162</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.3868</v>
+        <v>-1.4631</v>
       </c>
       <c r="M26" t="n">
-        <v>-20.7134</v>
+        <v>-20.4752</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.6007</v>
+        <v>-5.464399999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-15.1127</v>
+        <v>-15.011</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.939200000000001</v>
+        <v>-7.967000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-24.9519</v>
+        <v>-25.0396</v>
       </c>
       <c r="R26" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S26" t="n">
-        <v>2.449699999999999</v>
+        <v>3.251199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6616</v>
+        <v>2.6907</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2119000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.7032</v>
+        <v>-1.7057</v>
       </c>
       <c r="W26" t="n">
-        <v>7.520299999999999</v>
+        <v>7.483499999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.2234</v>
+        <v>-9.1891</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104525_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104525_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.798999999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104525_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.1891</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
